--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C776EA5-927C-450C-BF24-0904ABA71DDE}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C4154E8-48D7-4C91-B93B-763AE0F39642}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -769,6 +769,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -776,9 +779,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1120,8 +1120,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1137,13 +1137,13 @@
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="51"/>
+      <c r="A9" s="48"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="51"/>
+      <c r="A10" s="48"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
@@ -1367,11 +1367,6 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="E17:E31">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.47244094488188981" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1418,8 +1413,8 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
@@ -1435,13 +1430,13 @@
       <c r="E8" s="44"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="51"/>
+      <c r="A9" s="48"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="51"/>
+      <c r="A10" s="48"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
@@ -1632,7 +1627,7 @@
       <c r="E35" s="40"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="C36" s="32" t="s">
         <v>5</v>
       </c>
@@ -1666,7 +1661,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E17:E31">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C4154E8-48D7-4C91-B93B-763AE0F39642}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295E3F03-A33E-48F2-97FD-CBA100F10B53}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,6 +64,8 @@
     <definedName name="超過単価数量" localSheetId="1">'請求書（上下割　税抜）'!$B$18</definedName>
     <definedName name="超過単価単位" localSheetId="0">'請求書（上下割　税込）'!$C$18</definedName>
     <definedName name="超過単価単位" localSheetId="1">'請求書（上下割　税抜）'!$C$18</definedName>
+    <definedName name="適格請求書発行事業者登録番号" localSheetId="0">'請求書（上下割　税込）'!$C$14</definedName>
+    <definedName name="適格請求書発行事業者登録番号" localSheetId="1">'請求書（上下割　税抜）'!$C$14</definedName>
     <definedName name="内税" localSheetId="0">'請求書（上下割　税込）'!$E$34</definedName>
     <definedName name="名前" localSheetId="0">'請求書（上下割　税込）'!$D$5</definedName>
     <definedName name="名前" localSheetId="1">'請求書（上下割　税抜）'!$D$5</definedName>
@@ -666,9 +668,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -779,18 +778,16 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color theme="0"/>
@@ -1096,70 +1093,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
-      <c r="E3" s="20"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="48"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="4"/>
@@ -1171,9 +1168,9 @@
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1197,7 +1194,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="24"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1208,7 +1205,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1303,53 +1300,53 @@
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="45"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="45"/>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="44"/>
+      <c r="C34" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="39"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="46"/>
-      <c r="C36" s="32" t="s">
+      <c r="A36" s="45"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="39"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="47"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="41"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="C34:D35"/>
@@ -1365,6 +1362,7 @@
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1389,70 +1387,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
-      <c r="E3" s="20"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="50"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="48"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="48"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="4"/>
@@ -1464,9 +1462,9 @@
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1490,7 +1488,7 @@
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="24"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1501,7 +1499,7 @@
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
@@ -1596,53 +1594,53 @@
         <v>7</v>
       </c>
       <c r="B32" s="16"/>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="45"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="45"/>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="44"/>
+      <c r="C34" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="39"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="51"/>
-      <c r="C36" s="32" t="s">
+      <c r="A36" s="50"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="39"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="47"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="41"/>
+      <c r="A37" s="46"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="C36:D37"/>
     <mergeCell ref="E36:E37"/>
@@ -1658,10 +1656,11 @@
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="C34:D35"/>
     <mergeCell ref="E34:E35"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="E17:E31">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/FlowReport/Excelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295E3F03-A33E-48F2-97FD-CBA100F10B53}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6961685C-418A-4C67-8707-2FE66E4C2FF8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -776,11 +776,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1168,9 +1168,9 @@
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1462,9 +1462,9 @@
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1625,7 +1625,7 @@
       <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="50"/>
+      <c r="A36" s="51"/>
       <c r="C36" s="31" t="s">
         <v>5</v>
       </c>

--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/FlowReport/Excelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6961685C-418A-4C67-8707-2FE66E4C2FF8}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{290CF289-2341-4B49-97F0-5D7810FD57E1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -227,9 +227,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="177" formatCode="&quot;　請求金額 ： \ &quot;#,##0&quot;　&quot;;&quot;　請求金額 ： \ &quot;\-#,##0&quot;　&quot;"/>
     <numFmt numFmtId="178" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
     <numFmt numFmtId="179" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
+    <numFmt numFmtId="182" formatCode="&quot;　請求金額 ： &quot;&quot;¥&quot;\ #,##0;&quot;　請求金額 ： &quot;&quot;¥&quot;\ \-#,##0;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -625,9 +625,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -781,6 +778,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -810,10 +810,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1093,70 +1089,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
-      <c r="E3" s="19"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="46"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="46"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="4"/>
@@ -1164,186 +1160,186 @@
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6">
+      <c r="A14" s="51">
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="24"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="16"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="31" t="s">
+      <c r="B32" s="15"/>
+      <c r="C32" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="26"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
-      <c r="C34" s="27" t="s">
+      <c r="A34" s="43"/>
+      <c r="C34" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="37"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="39"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="38"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="45"/>
-      <c r="C36" s="31" t="s">
+      <c r="A36" s="44"/>
+      <c r="C36" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="38"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="37"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="40"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1387,70 +1383,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
-      <c r="E3" s="19"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="49"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="47"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
+      <c r="A9" s="46"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="47"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
+      <c r="A10" s="46"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="4"/>
@@ -1458,186 +1454,186 @@
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6">
+      <c r="A14" s="51">
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="17"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="17"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="24"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="17"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="17"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="17"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="17"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="17"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="17"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="17"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="17"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="16"/>
     </row>
     <row r="27" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="17"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="17"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="17"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="17"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="17"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="31" t="s">
+      <c r="B32" s="15"/>
+      <c r="C32" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="44"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="26"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="44"/>
-      <c r="C34" s="27" t="s">
+      <c r="A34" s="43"/>
+      <c r="C34" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="37"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="39"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="38"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="51"/>
-      <c r="C36" s="31" t="s">
+      <c r="A36" s="50"/>
+      <c r="C36" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="38"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="37"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="46"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="40"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/FlowReport/Excelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{290CF289-2341-4B49-97F0-5D7810FD57E1}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DEB2BB7-76EA-4CC8-BF37-8C908446EA3C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書（上下割　税込）" sheetId="1" r:id="rId1"/>
@@ -225,11 +225,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="178" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
-    <numFmt numFmtId="179" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
-    <numFmt numFmtId="182" formatCode="&quot;　請求金額 ： &quot;&quot;¥&quot;\ #,##0;&quot;　請求金額 ： &quot;&quot;¥&quot;\ \-#,##0;"/>
+    <numFmt numFmtId="177" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="178" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
+    <numFmt numFmtId="179" formatCode="&quot;　請求金額 ： &quot;&quot;¥&quot;\ #,##0;&quot;　請求金額 ： &quot;&quot;¥&quot;\ \-#,##0;"/>
+    <numFmt numFmtId="180" formatCode="&quot;　&quot;yyyy&quot;年&quot;mm&quot;月&quot;dd&quot;日&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -605,7 +606,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -677,11 +678,11 @@
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -691,6 +692,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -731,7 +735,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -747,7 +751,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
@@ -755,7 +759,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -779,8 +783,12 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -810,6 +818,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1089,65 +1101,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="46"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="46"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="17"/>
@@ -1160,13 +1172,13 @@
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="51">
+      <c r="A14" s="24">
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1296,50 +1308,50 @@
         <v>7</v>
       </c>
       <c r="B32" s="15"/>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="43"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="13"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="25"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="43"/>
-      <c r="C34" s="26" t="s">
+      <c r="A34" s="44"/>
+      <c r="C34" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="37"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="21"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="38"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="44"/>
-      <c r="C36" s="30" t="s">
+      <c r="A36" s="45"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="37"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="45"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="19"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="39"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1383,65 +1395,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
       <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" ht="24" x14ac:dyDescent="0.15">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="46"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
+      <c r="A9" s="47"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="46"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
+      <c r="A10" s="47"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="17"/>
@@ -1454,13 +1466,13 @@
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="51">
+      <c r="A14" s="24">
         <f>E36</f>
         <v>0</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:5" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="16" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1590,50 +1602,50 @@
         <v>7</v>
       </c>
       <c r="B32" s="15"/>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="25"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="43"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="13"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="25"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="43"/>
-      <c r="C34" s="26" t="s">
+      <c r="A34" s="53"/>
+      <c r="C34" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="37"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="21"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="38"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="50"/>
-      <c r="C36" s="30" t="s">
+      <c r="A36" s="51"/>
+      <c r="C36" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="37"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="45"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="19"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="39"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/public/請求書デフォルトテンプレート.xlsx
+++ b/public/請求書デフォルトテンプレート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a630334910042c28/Desktop/FlowTech/FlowReport/Excelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DEB2BB7-76EA-4CC8-BF37-8C908446EA3C}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{86700753-E3D2-4BF2-9CC8-4F98E3B6770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3692B26-3752-40C0-B0F4-8DDF78B32132}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,12 +225,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="&quot;　&quot;yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;"/>
     <numFmt numFmtId="178" formatCode="[&lt;=999]000;[&lt;=9999]000\-00;000\-0000"/>
     <numFmt numFmtId="179" formatCode="&quot;　請求金額 ： &quot;&quot;¥&quot;\ #,##0;&quot;　請求金額 ： &quot;&quot;¥&quot;\ \-#,##0;"/>
-    <numFmt numFmtId="180" formatCode="&quot;　&quot;yyyy&quot;年&quot;mm&quot;月&quot;dd&quot;日&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -606,7 +605,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -782,13 +781,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1401,8 +1393,8 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C2" s="4"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D3" s="1"/>
@@ -1609,14 +1601,14 @@
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="53"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="13"/>
       <c r="C33" s="35"/>
       <c r="D33" s="36"/>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="53"/>
+      <c r="A34" s="44"/>
       <c r="C34" s="27" t="s">
         <v>14</v>
       </c>
